--- a/excel/testdata/raw_cells/raw_cells_tests.xlsx
+++ b/excel/testdata/raw_cells/raw_cells_tests.xlsx
@@ -66,10 +66,10 @@
   </numFmts>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
